--- a/data/trans_orig/P16A09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33943</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451362</t>
+          <t>453248</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468260</t>
+          <t>468264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287338</t>
+          <t>286883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301202</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746514</t>
+          <t>746765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766587</t>
+          <t>766778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23107</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357017</t>
+          <t>357073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365195</t>
+          <t>365214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354127</t>
+          <t>354894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368303</t>
+          <t>368223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>715692</t>
+          <t>716189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731886</t>
+          <t>732189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23890</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37307</t>
+          <t>38826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518499</t>
+          <t>518608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534352</t>
+          <t>534090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148036</t>
+          <t>147306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162365</t>
+          <t>162188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672864</t>
+          <t>671345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692906</t>
+          <t>692974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>41183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67623</t>
+          <t>68589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67130</t>
+          <t>66253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1170711</t>
+          <t>1169745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1197640</t>
+          <t>1197151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674445</t>
+          <t>673526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>695285</t>
+          <t>694357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1852124</t>
+          <t>1850937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1885490</t>
+          <t>1886367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40994</t>
+          <t>42195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>53357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332857</t>
+          <t>332547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344281</t>
+          <t>344259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527758</t>
+          <t>526557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548823</t>
+          <t>548598</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865619</t>
+          <t>864932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890882</t>
+          <t>889468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>66099</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104530</t>
+          <t>102211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +2498,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>84163</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>67026</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>101294</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>84163</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>67911</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>102860</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293725</t>
+          <t>292580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1144230</t>
+          <t>1146549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1180823</t>
+          <t>1182661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +2611,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1462797</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1445666</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1479934</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1462</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1462797</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1444100</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1479049</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>94,56%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77902</t>
+          <t>77395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115691</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148105</t>
+          <t>149057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>198511</t>
+          <t>198522</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>234446</t>
+          <t>235805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299592</t>
+          <t>300256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3153481</t>
+          <t>3152007</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3191270</t>
+          <t>3191777</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3179613</t>
+          <t>3179602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3230019</t>
+          <t>3229067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6347704</t>
+          <t>6347040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6412850</t>
+          <t>6411491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415170</t>
+          <t>415766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431977</t>
+          <t>431971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303397</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313160</t>
+          <t>313353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724599</t>
+          <t>723060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743290</t>
+          <t>742192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401561</t>
+          <t>402444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413929</t>
+          <t>413805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319342</t>
+          <t>318919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331334</t>
+          <t>331255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727938</t>
+          <t>727648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743177</t>
+          <t>743996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602265</t>
+          <t>600757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619103</t>
+          <t>619673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239003</t>
+          <t>237396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252802</t>
+          <t>252849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>845294</t>
+          <t>846714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>868531</t>
+          <t>869382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38980</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,82 +4412,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22900</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14399</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32709</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>49920</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>37223</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>64885</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22900</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14555</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33722</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>49920</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>38034</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>66467</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1118335</t>
+          <t>1118524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1140124</t>
+          <t>1139564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,82 +4525,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>743757</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>733948</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>752258</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1874053</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1859088</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1886750</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>96,63%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>743757</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>732935</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>752102</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1745</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1874053</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1857506</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1885939</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40058</t>
+          <t>39911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68203</t>
+          <t>67497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48882</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80408</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490185</t>
+          <t>488863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504095</t>
+          <t>504021</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>689126</t>
+          <t>689832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>717271</t>
+          <t>717418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1187517</t>
+          <t>1185914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1219043</t>
+          <t>1217468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87523</t>
+          <t>88847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128474</t>
+          <t>130161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88829</t>
+          <t>90579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131025</t>
+          <t>131701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263916</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>976782</t>
+          <t>975095</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1017733</t>
+          <t>1016409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1240073</t>
+          <t>1239397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1282269</t>
+          <t>1280519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>54149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91214</t>
+          <t>91263</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>177579</t>
+          <t>178404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>234936</t>
+          <t>233981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244115</t>
+          <t>244133</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>314381</t>
+          <t>311081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3323105</t>
+          <t>3323056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3359438</t>
+          <t>3360170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3302014</t>
+          <t>3302969</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3359371</t>
+          <t>3358546</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6636888</t>
+          <t>6640188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6707154</t>
+          <t>6707136</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420003</t>
+          <t>421138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428360</t>
+          <t>428359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336583</t>
+          <t>336566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345955</t>
+          <t>345952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>761948</t>
+          <t>762743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773059</t>
+          <t>773255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377227</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360658</t>
+          <t>361626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371144</t>
+          <t>371125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738563</t>
+          <t>738931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748351</t>
+          <t>748357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21450</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510856</t>
+          <t>511774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520975</t>
+          <t>520776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151694</t>
+          <t>152562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164048</t>
+          <t>164018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>666586</t>
+          <t>668332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682684</t>
+          <t>682812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54489</t>
+          <t>54670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114032</t>
+          <t>1112974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134208</t>
+          <t>1134486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>800093</t>
+          <t>801215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>817082</t>
+          <t>818029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1921025</t>
+          <t>1920844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1946668</t>
+          <t>1947890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31036</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57517</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43189</t>
+          <t>43726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72483</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598521</t>
+          <t>598291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612201</t>
+          <t>612811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680727</t>
+          <t>680037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>707208</t>
+          <t>706984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1286467</t>
+          <t>1285588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1315761</t>
+          <t>1315224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45112</t>
+          <t>46159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77922</t>
+          <t>78478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45502</t>
+          <t>44638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76136</t>
+          <t>76439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1004103</t>
+          <t>1003547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1036913</t>
+          <t>1035866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1293034</t>
+          <t>1292731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1323668</t>
+          <t>1324532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33092</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108733</t>
+          <t>109126</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157934</t>
+          <t>155476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>151249</t>
+          <t>151754</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207597</t>
+          <t>208171</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3326222</t>
+          <t>3326260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3352630</t>
+          <t>3352027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3373662</t>
+          <t>3376120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3422863</t>
+          <t>3422470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6709721</t>
+          <t>6709147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6766069</t>
+          <t>6765564</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>19268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495823</t>
+          <t>495710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503355</t>
+          <t>503551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427587</t>
+          <t>428199</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439305</t>
+          <t>439427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927166</t>
+          <t>926421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941236</t>
+          <t>941090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440008</t>
+          <t>439645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449749</t>
+          <t>449717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359242</t>
+          <t>359376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371523</t>
+          <t>371463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>803491</t>
+          <t>803801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>819038</t>
+          <t>819209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>23027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>647490</t>
+          <t>647533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665348</t>
+          <t>665797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143461</t>
+          <t>143884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158517</t>
+          <t>158178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>795644</t>
+          <t>796649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824925</t>
+          <t>825727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37548</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65524</t>
+          <t>66837</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>996555</t>
+          <t>996507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1015396</t>
+          <t>1015280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942779</t>
+          <t>940751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>966850</t>
+          <t>965564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945776</t>
+          <t>1944463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975172</t>
+          <t>1975331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17613</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42736</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78426</t>
+          <t>79450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>54316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89503</t>
+          <t>90096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455946</t>
+          <t>455626</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466746</t>
+          <t>466789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>760570</t>
+          <t>759546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>796260</t>
+          <t>795866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1223052</t>
+          <t>1222459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258593</t>
+          <t>1258239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47086</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67150</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45402</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68419</t>
+          <t>69031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>693002</t>
+          <t>690964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>713066</t>
+          <t>712981</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>932240</t>
+          <t>931628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>955257</t>
+          <t>954797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74937</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148099</t>
+          <t>144772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207016</t>
+          <t>207958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203662</t>
+          <t>201253</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275006</t>
+          <t>270720</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3298921</t>
+          <t>3300147</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3329909</t>
+          <t>3330162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3365412</t>
+          <t>3364470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3424329</t>
+          <t>3427656</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6671280</t>
+          <t>6675566</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6742624</t>
+          <t>6745033</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>20620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>33656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453248</t>
+          <t>453156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468264</t>
+          <t>467795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286883</t>
+          <t>287141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>301443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>746765</t>
+          <t>746801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766778</t>
+          <t>766940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>23912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357073</t>
+          <t>356962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365214</t>
+          <t>365181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354894</t>
+          <t>354665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368223</t>
+          <t>368276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>716189</t>
+          <t>714887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732189</t>
+          <t>731482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>39046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518608</t>
+          <t>518505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534090</t>
+          <t>533420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147306</t>
+          <t>148700</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162188</t>
+          <t>162328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671345</t>
+          <t>671125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692974</t>
+          <t>693281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41183</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68589</t>
+          <t>69102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40759</t>
+          <t>39886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66253</t>
+          <t>64762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>99774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1169745</t>
+          <t>1169232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1197151</t>
+          <t>1196879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>673526</t>
+          <t>674399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>694357</t>
+          <t>695513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1850937</t>
+          <t>1852846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886367</t>
+          <t>1887858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>18908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42195</t>
+          <t>41053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>29012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53357</t>
+          <t>53165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332547</t>
+          <t>333258</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344259</t>
+          <t>344666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526557</t>
+          <t>527699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548598</t>
+          <t>549844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>864932</t>
+          <t>865124</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>889468</t>
+          <t>889277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66099</t>
+          <t>66739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102211</t>
+          <t>102540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67026</t>
+          <t>66058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101294</t>
+          <t>101639</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292580</t>
+          <t>294203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1146549</t>
+          <t>1146220</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1182661</t>
+          <t>1182021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1445666</t>
+          <t>1445321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1479934</t>
+          <t>1480902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77395</t>
+          <t>78458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117165</t>
+          <t>117945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149057</t>
+          <t>147818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>198522</t>
+          <t>199668</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>235805</t>
+          <t>237447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300256</t>
+          <t>303552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3152007</t>
+          <t>3151227</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3191777</t>
+          <t>3190714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3179602</t>
+          <t>3178456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3229067</t>
+          <t>3230306</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6347040</t>
+          <t>6343744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6411491</t>
+          <t>6409849</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415766</t>
+          <t>416096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431971</t>
+          <t>431787</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313353</t>
+          <t>313336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>723060</t>
+          <t>725581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>742192</t>
+          <t>743176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402444</t>
+          <t>403325</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413805</t>
+          <t>413953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318919</t>
+          <t>320012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331255</t>
+          <t>331283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727648</t>
+          <t>729046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743996</t>
+          <t>744039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600757</t>
+          <t>601704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619673</t>
+          <t>619023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237396</t>
+          <t>238170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252849</t>
+          <t>252860</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>846714</t>
+          <t>847039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>869382</t>
+          <t>868779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32709</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64885</t>
+          <t>64295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1118524</t>
+          <t>1118419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1139564</t>
+          <t>1139362</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>733948</t>
+          <t>733104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>752258</t>
+          <t>752200</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1859088</t>
+          <t>1859678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886750</t>
+          <t>1886796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39911</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>66620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>49207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82011</t>
+          <t>80926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488863</t>
+          <t>489464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504021</t>
+          <t>504146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>689832</t>
+          <t>690709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>717418</t>
+          <t>717510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1185914</t>
+          <t>1186999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1217468</t>
+          <t>1218718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88847</t>
+          <t>88357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>130161</t>
+          <t>130218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90579</t>
+          <t>88577</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131701</t>
+          <t>130334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>975095</t>
+          <t>975038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1016409</t>
+          <t>1016899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1239397</t>
+          <t>1240764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1280519</t>
+          <t>1282521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>54908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91263</t>
+          <t>91894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178404</t>
+          <t>178253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233981</t>
+          <t>237844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244133</t>
+          <t>244023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311081</t>
+          <t>311940</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3323056</t>
+          <t>3322425</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3360170</t>
+          <t>3359411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3302969</t>
+          <t>3299106</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3358546</t>
+          <t>3358697</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6640188</t>
+          <t>6639329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6707136</t>
+          <t>6707246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421138</t>
+          <t>420943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428359</t>
+          <t>428357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336566</t>
+          <t>336610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345952</t>
+          <t>345954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>762743</t>
+          <t>761645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773255</t>
+          <t>773032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361626</t>
+          <t>362402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371125</t>
+          <t>371246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748357</t>
+          <t>748471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511774</t>
+          <t>512125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520776</t>
+          <t>520980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152562</t>
+          <t>151610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164018</t>
+          <t>163978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>668332</t>
+          <t>668061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682812</t>
+          <t>682887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27624</t>
+          <t>26532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54670</t>
+          <t>52556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1112974</t>
+          <t>1114032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134486</t>
+          <t>1133931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>801215</t>
+          <t>801186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>818029</t>
+          <t>816984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920844</t>
+          <t>1922958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947890</t>
+          <t>1948982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58207</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43726</t>
+          <t>44057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73362</t>
+          <t>74677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598291</t>
+          <t>598331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612811</t>
+          <t>612747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680037</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>706984</t>
+          <t>707122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1285588</t>
+          <t>1284273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1315224</t>
+          <t>1314893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>45552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78478</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44638</t>
+          <t>45183</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76439</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1003547</t>
+          <t>1004855</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1035866</t>
+          <t>1036473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1292731</t>
+          <t>1292203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1324532</t>
+          <t>1323987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59462</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109126</t>
+          <t>110166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155476</t>
+          <t>157081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>151754</t>
+          <t>152224</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208171</t>
+          <t>207539</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3326260</t>
+          <t>3326056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3352027</t>
+          <t>3352319</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3376120</t>
+          <t>3374515</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3422470</t>
+          <t>3421430</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6709147</t>
+          <t>6709779</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6765564</t>
+          <t>6765094</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -8633,102 +8633,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14553</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9489</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23957</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>19501</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>12878</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>28505</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12912</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8040</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19268</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>17433</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>11589</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>26258</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -8746,102 +8746,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500690</t>
+          <t>545670</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495710</t>
+          <t>538672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503551</t>
+          <t>548556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>473858</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>464454</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>478922</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1019528</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1010524</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1026151</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>98,12%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>434555</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>428199</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>439427</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>935246</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>926421</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>941090</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21450</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>16356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>446164</t>
+          <t>476773</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>439645</t>
+          <t>469208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449717</t>
+          <t>480354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>366304</t>
+          <t>405549</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359376</t>
+          <t>398577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371463</t>
+          <t>411406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>812467</t>
+          <t>882322</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>803801</t>
+          <t>872970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>819209</t>
+          <t>889126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>25934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>39340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>658030</t>
+          <t>460703</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>647533</t>
+          <t>452243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665797</t>
+          <t>465904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>153039</t>
+          <t>171840</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143884</t>
+          <t>161563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158178</t>
+          <t>177814</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>811069</t>
+          <t>632543</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>796649</t>
+          <t>619769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825727</t>
+          <t>641011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>29323</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51704</t>
+          <t>58434</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>46704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66837</t>
+          <t>72449</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -9775,22 +9775,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1007243</t>
+          <t>1101921</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>996507</t>
+          <t>1089912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1015280</t>
+          <t>1110938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>952352</t>
+          <t>830961</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>940751</t>
+          <t>821649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965564</t>
+          <t>838640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1959596</t>
+          <t>1932883</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1944463</t>
+          <t>1918868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975331</t>
+          <t>1944613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034103</t>
+          <t>1131032</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034103</t>
+          <t>1131032</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034103</t>
+          <t>1131032</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011300</t>
+          <t>1991317</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011300</t>
+          <t>1991317</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011300</t>
+          <t>1991317</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58530</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>48770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79450</t>
+          <t>73449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>69677</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54316</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90096</t>
+          <t>85225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>462412</t>
+          <t>554084</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455626</t>
+          <t>546332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466789</t>
+          <t>559357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>780466</t>
+          <t>770554</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>759546</t>
+          <t>756678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>795866</t>
+          <t>781357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1242878</t>
+          <t>1324638</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1222459</t>
+          <t>1311383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258239</t>
+          <t>1337086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>63216</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47171</t>
+          <t>51208</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>76875</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>63216</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>76321</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>703695</t>
+          <t>779777</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>690964</t>
+          <t>766118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>712981</t>
+          <t>791785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>944202</t>
+          <t>1017005</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>931628</t>
+          <t>1003900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>954797</t>
+          <t>1027880</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>58811</t>
+          <t>63805</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43696</t>
+          <t>50416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73711</t>
+          <t>80871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>182017</t>
+          <t>199043</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144772</t>
+          <t>177650</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207958</t>
+          <t>221210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>240829</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>201253</t>
+          <t>236404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270720</t>
+          <t>293616</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3315047</t>
+          <t>3376378</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3300147</t>
+          <t>3359312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3330162</t>
+          <t>3389767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3390411</t>
+          <t>3432539</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3364470</t>
+          <t>3410372</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3427656</t>
+          <t>3453932</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6705457</t>
+          <t>6808917</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6675566</t>
+          <t>6778149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6745033</t>
+          <t>6835361</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373858</t>
+          <t>3440183</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373858</t>
+          <t>3440183</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373858</t>
+          <t>3440183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572428</t>
+          <t>3631582</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572428</t>
+          <t>3631582</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572428</t>
+          <t>3631582</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6946286</t>
+          <t>7071765</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6946286</t>
+          <t>7071765</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6946286</t>
+          <t>7071765</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
